--- a/stories/arbres/ATOM-TMP.MET.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -823,6 +823,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -837,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1131,6 +1143,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1155,7 +1172,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait froid. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues. Papa dit : pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau. Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
+          <t>Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait froid. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues. Pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau. Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1293,6 +1310,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait froid. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues.
+papa|Pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau.
+narrateur|Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1497,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il pleut, puis il fait froid. Que met Jules ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a mis les bottes sous la pluie. Puis le manteau quand il faisait froid. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Jules range ses bottes. Papa ouvre la porte de l'école.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-03.xlsx
@@ -849,7 +849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,7 @@
 narrateur|Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1504,6 +1510,7 @@
           <t>narrateur|Il pleut, puis il fait froid. Que met Jules ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1682,7 @@
           <t>narrateur|Jules a mis les bottes sous la pluie. Puis le manteau quand il faisait froid. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1846,7 @@
           <t>narrateur|Jules range ses bottes. Papa ouvre la porte de l'école.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2014,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2057,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2272,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules met manteau et bottes</t>
+          <t>Le pain dans la neige fondue</t>
         </is>
       </c>
     </row>
@@ -835,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina veut le pain chaud chez le voisin. La neige fond. Il pleut. Le sac se mouille. Ils le protègent. Le pain sent encore le four.</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait froid. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues. Pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau. Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
+          <t>La neige fond en filets gris sur le trottoir. Une gouttière du voisin verse dans une flaque sale. L'air sent le pain, déjà, très loin. Nina vit ici, avec papa. La maison du voisin a une fenêtre jaune. De la vapeur y danse. Tu as senti le pain ? Oui, papa. Je veux y aller. Il pleut sur la neige fondue. On se couvre ? En ce moment, Nina prend le manteau lourd. Il sent la laine mouillée d'hier. Papa tend les bottes. Nina les enfile. La neige fondue fait un bruit mou sous la porte. C'est glissant. On va doucement. Ils sortent. La pluie pique les capuches. Les filets gris courent vers le caniveau. Nina donne la main à papa. Le sac en toile pend à son poignet. Devant chez le voisin, trois marches luisent. Tu montes ? Nina pose un pied. La neige fondue fuit sous la botte. Oups. Je te tiens. Elle gravit les marches. Papa frappe. La porte s'ouvre sur la vapeur. Le pain est là, trop chaud pour les mains. Il sent le four ! Merci. Nina tend le sac. Le voisin y glisse le pain. Une goutte de pluie tombe dans le sac. Le sac est mouillé. On le serre contre le manteau ? Nina presse le sac contre elle. Le pain reste au chaud, à l'abri. Bravo. Tu l'as protégé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues. Papa dit : pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau. Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La neige fond en filets gris sur le trottoir. Une gouttière du voisin verse dans une flaque sale. L'air sent le pain, déjà, très loin. Nina vit ici, avec papa. La maison du voisin a une fenêtre jaune. De la vapeur y danse. Tu as senti le pain ? Oui, papa. Je veux y aller. Il pleut sur la neige fondue. On se couvre ? En ce moment, Nina prend le manteau lourd. Il sent la laine mouillée d'hier. Papa tend les bottes. Nina les enfile. La neige fondue fait un bruit mou sous la porte. C'est glissant. On va doucement. Ils sortent. La pluie pique les capuches. Les filets gris courent vers le caniveau. Nina donne la main à papa. Le sac en toile pend à son poignet. Devant chez le voisin, trois marches luisent. Tu montes ? Nina pose un pied. La neige fondue fuit sous la botte. Oups. Je te tiens. Elle gravit les marches. Papa frappe. La porte s'ouvre sur la vapeur. Le pain est là, trop chaud pour les mains. Il sent le four ! Merci. Nina tend le sac. Le voisin y glisse le pain. Une goutte de pluie tombe dans le sac. Le sac est mouillé. On le serre contre le manteau ? Nina presse le sac contre elle. Le pain reste au chaud, à l'abri. Bravo. Tu l'as protégé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,7 +1257,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1317,12 +1329,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules ouvre la porte du jardin avec papa. Il y a de la pluie. Papa prend les bottes. Jules met les bottes. Ses pieds sont au sec. Ils coupent du persil. L'herbe est mouillée. Plus tard, le vent arrive. Il fait froid. Ils vont à l'école. Papa prend le manteau. Jules enfile le manteau. Devant l'école, l'air pique les joues.
-papa|Pluie, les bottes. Froid, le manteau. Il y a quatre saisons. Printemps, des fleurs. Été, il fait chaud. Automne, des feuilles. Hiver, le manteau.
-narrateur|Un signe chacune. Au jardin, puis à l'école, on s'habille selon le temps. Jules touche son manteau. Il touche ses bottes. Papa tient sa main.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La neige fond en filets gris sur le trottoir.
+narrateur|Une gouttière du voisin verse dans une flaque sale.
+narrateur|L'air sent le pain, déjà, très loin.
+narrateur|Nina vit ici, avec papa.
+narrateur|La maison du voisin a une fenêtre jaune.
+narrateur|De la vapeur y danse.
+papa|Tu as senti le pain ?
+enfant-f|Oui, papa.
+enfant-f|Je veux y aller.
+papa|Il pleut sur la neige fondue.
+papa|On se couvre ?
+narrateur|En ce moment, Nina prend le manteau lourd.
+narrateur|Il sent la laine mouillée d'hier.
+narrateur|Papa tend les bottes.
+narrateur|Nina les enfile.
+narrateur|La neige fondue fait un bruit mou sous la porte.
+enfant-f|C'est glissant.
+papa|On va doucement.
+narrateur|Ils sortent.
+narrateur|La pluie pique les capuches.
+narrateur|Les filets gris courent vers le caniveau.
+narrateur|Nina donne la main à papa.
+narrateur|Le sac en toile pend à son poignet.
+narrateur|Devant chez le voisin, trois marches luisent.
+papa|Tu montes ?
+narrateur|Nina pose un pied.
+narrateur|La neige fondue fuit sous la botte.
+enfant-f|Oups.
+papa|Je te tiens.
+narrateur|Elle gravit les marches.
+narrateur|Papa frappe.
+narrateur|La porte s'ouvre sur la vapeur.
+narrateur|Le pain est là, trop chaud pour les mains.
+enfant-f|Il sent le four !
+papa|Merci.
+narrateur|Nina tend le sac.
+narrateur|Le voisin y glisse le pain.
+narrateur|Une goutte de pluie tombe dans le sac.
+enfant-f|Le sac est mouillé.
+papa|On le serre contre le manteau ?
+narrateur|Nina presse le sac contre elle.
+narrateur|Le pain reste au chaud, à l'abri.
+papa|Bravo.
+papa|Tu l'as protégé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1347,12 +1399,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il pleut, puis il fait froid. Que met Jules ?</t>
+          <t>Il pleut, et la neige fond. Que met Nina ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Il pleut, puis il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Que met Jules ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il pleut, et la neige fond. Que met Nina ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1382,7 +1434,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Pluie, les bottes. Froid, le manteau. Que met-on ?</t>
+          <t>Pluie et neige fondue. Que met-on ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1424,14 +1476,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1559,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il pleut, puis il fait froid. Que met Jules ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il pleut, et la neige fond.
+narrateur|Que met Nina ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jules a mis les bottes sous la pluie. Puis le manteau quand il faisait froid. Papa était là.</t>
+          <t>Ils redescendent les marches. Nina tient le sac très fort. Il est encore chaud. Oui. On rentre avant qu'il refroidisse. La pluie a grossi les filets gris. Une flaque barre le trottoir. On la contourne ? Oui. Nina marche au bord. Ses bottes restent au sec, presque. Le manteau lourd fume un peu. Chez eux, papa ouvre. L'air de la cuisine est plus doux. Nina pose le sac sur la table. Le pain a une croûte dorée. Pas mouillé ! Tu l'as bien tenu. Papa coupe une tranche. La mie fume. C'est pour nous. Oui. Après la neige fondue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules a mis les bottes sous la pluie. Puis le manteau quand il faisait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils redescendent les marches. Nina tient le sac très fort. Il est encore chaud. Oui. On rentre avant qu'il refroidisse. La pluie a grossi les filets gris. Une flaque barre le trottoir. On la contourne ? Oui. Nina marche au bord. Ses bottes restent au sec, presque. Le manteau lourd fume un peu. Chez eux, papa ouvre. L'air de la cuisine est plus doux. Nina pose le sac sur la table. Le pain a une croûte dorée. Pas mouillé ! Tu l'as bien tenu. Papa coupe une tranche. La mie fume. C'est pour nous. Oui. Après la neige fondue.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1655,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1731,31 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jules a mis les bottes sous la pluie. Puis le manteau quand il faisait froid. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Ils redescendent les marches.
+narrateur|Nina tient le sac très fort.
+enfant-f|Il est encore chaud.
+papa|Oui.
+papa|On rentre avant qu'il refroidisse.
+narrateur|La pluie a grossi les filets gris.
+narrateur|Une flaque barre le trottoir.
+papa|On la contourne ?
+enfant-f|Oui.
+narrateur|Nina marche au bord.
+narrateur|Ses bottes restent au sec, presque.
+narrateur|Le manteau lourd fume un peu.
+narrateur|Chez eux, papa ouvre.
+narrateur|L'air de la cuisine est plus doux.
+narrateur|Nina pose le sac sur la table.
+narrateur|Le pain a une croûte dorée.
+enfant-f|Pas mouillé !
+papa|Tu l'as bien tenu.
+narrateur|Papa coupe une tranche.
+narrateur|La mie fume.
+enfant-f|C'est pour nous.
+papa|Oui.
+papa|Après la neige fondue.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1780,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Jules range ses bottes. Papa ouvre la porte de l'école.</t>
+          <t>Nina range les bottes près de la porte. De la neige fondue s'égoutte encore. Le manteau au crochet ? Oui. Le pain attend, déjà entamé. La fenêtre du voisin est encore jaune.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jules range ses bottes. Papa ouvre la porte de l'école.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range les bottes près de la porte. De la neige fondue s'égoutte encore. Le manteau au crochet ? Oui. Le pain attend, déjà entamé. La fenêtre du voisin est encore jaune.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1848,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1843,10 +1916,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Jules range ses bottes. Papa ouvre la porte de l'école.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina range les bottes près de la porte.
+narrateur|De la neige fondue s'égoutte encore.
+papa|Le manteau au crochet ?
+enfant-f|Oui.
+narrateur|Le pain attend, déjà entamé.
+narrateur|La fenêtre du voisin est encore jaune.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1871,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La croûte craque sous les dents. Dehors, les filets gris courent encore. Il est chaud. Oui. Le sac mouillé sèche sur la chaise.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La croûte craque sous les dents. Dehors, les filets gris courent encore. Il est chaud. Oui. Le sac mouillé sèche sur la chaise.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1939,7 +2016,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2011,10 +2088,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|La croûte craque sous les dents.
+narrateur|Dehors, les filets gris courent encore.
+enfant-f|Il est chaud.
+papa|Oui.
+narrateur|Le sac mouillé sèche sur la chaise.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2033,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2071,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-03.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-03.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin puis école</t>
+          <t>trottoir de neige fondue, maison du voisin</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jules, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>
